--- a/event_registration_forms/049_photography_release_consent_form--event_registration_forms.xlsx
+++ b/event_registration_forms/049_photography_release_consent_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_1</t>
+          <t>client_consent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>client_consent</t>
+          <t>Client Consent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_2</t>
+          <t>event_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>usage_rights</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Event Details</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe the event</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +570,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_3</t>
+          <t>photographer_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>client_info</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Photographer's Information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provide your name, email, and contact number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,87 +597,95 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_4</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>photographer_signature</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Provide a valid phone number and email</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_5</t>
+          <t>photo_release_consent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>client_signature</t>
+          <t>Photo Release Consent</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_6</t>
+          <t>photo_usage_rights</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Photo Usage Rights</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_7</t>
+          <t>photo_credit_line</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>photo_release_consent</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Photo Credit Line</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Include your name and role</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +697,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_8</t>
+          <t>photographer_contact_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>usage_rights_notes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Photographer's Contact Number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A valid phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +724,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_9</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>photographer_info</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A valid email address</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>photo_usage_rights</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_11</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>photo_credit_line</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Event Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HH -MM</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +805,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_12</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>photographer</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Event Location</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Provide the venue name and address</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,110 +832,130 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_13</t>
+          <t>event_description</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Event Description</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Briefly describe the event</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_14</t>
+          <t>date_taken</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Date Taken</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_15</t>
+          <t>time_taken</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Time Taken</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HH -MM</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_16</t>
+          <t>photographer_info_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Photographer's Information (Additional)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Provide any additional details</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_17</t>
+          <t>photo_credit_line_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>event_time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Photo Credit Line 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Include your name and role</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +967,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_18</t>
+          <t>photographer_contact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Photographer's Contact</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A valid phone number</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>event_description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>date_taken</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time_taken</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>photographer_info</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>photo_credit_line</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>event_registration_forms_photography_release_consent_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>photographer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +997,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,119 +1025,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_7_choices</t>
+          <t>client_consent_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_7_choices</t>
+          <t>client_consent_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10_choices</t>
+          <t>client_consent_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Print'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10_choices</t>
+          <t>photo_release_consent_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'web'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Web'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10_choices</t>
+          <t>photo_release_consent_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10_choices</t>
+          <t>photo_usage_rights_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_registration_forms_photography_release_consent_form_10_choices</t>
+          <t>photo_usage_rights_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>photo_usage_rights_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>photo_usage_rights_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>photo_usage_rights_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
